--- a/app/content/shumian.xlsx
+++ b/app/content/shumian.xlsx
@@ -1020,7 +1020,7 @@
         <v>急击</v>
       </c>
       <c r="C2" t="str">
-        <v>威</v>
+        <v>器</v>
       </c>
       <c r="D2" t="str">
         <v>乘其无甲，凿穿敌阵。</v>
@@ -1043,7 +1043,7 @@
         <v>缓图</v>
       </c>
       <c r="C3" t="str">
-        <v>理</v>
+        <v>隐</v>
       </c>
       <c r="D3" t="str">
         <v>依险列阵，耗其锐气。</v>
@@ -1066,7 +1066,7 @@
         <v>断其归路</v>
       </c>
       <c r="C4" t="str">
-        <v>利</v>
+        <v>策</v>
       </c>
       <c r="D4" t="str">
         <v>绕袭敌后，绝其取甲之念。</v>
@@ -1089,7 +1089,7 @@
         <v>放其生路</v>
       </c>
       <c r="C5" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D5" t="str">
         <v>围三阙一，乱其军心。</v>
@@ -1112,7 +1112,7 @@
         <v>死守</v>
       </c>
       <c r="C6" t="str">
-        <v>理</v>
+        <v>器</v>
       </c>
       <c r="D6" t="str">
         <v>兵寡粮薄，以身作旗。</v>
@@ -1135,7 +1135,7 @@
         <v>夜遁</v>
       </c>
       <c r="C7" t="str">
-        <v>威</v>
+        <v>隐</v>
       </c>
       <c r="D7" t="str">
         <v>无旗无饰的普通马车，往西。</v>
@@ -1158,7 +1158,7 @@
         <v>楚歌</v>
       </c>
       <c r="C8" t="str">
-        <v>情</v>
+        <v>隐</v>
       </c>
       <c r="D8" t="str">
         <v>四面唱起楚地民谣。</v>
@@ -1181,7 +1181,7 @@
         <v>耗其心气</v>
       </c>
       <c r="C9" t="str">
-        <v>理</v>
+        <v>策</v>
       </c>
       <c r="D9" t="str">
         <v>围而不攻，步步为营。</v>
@@ -1204,7 +1204,7 @@
         <v>劝降</v>
       </c>
       <c r="C10" t="str">
-        <v>利</v>
+        <v>器</v>
       </c>
       <c r="D10" t="str">
         <v>降者不杀，去者不禁。</v>
@@ -1227,7 +1227,7 @@
         <v>全其体面</v>
       </c>
       <c r="C11" t="str">
-        <v>情</v>
+        <v>策</v>
       </c>
       <c r="D11" t="str">
         <v>给末路英雄，留最后一份敬意。</v>
@@ -1391,7 +1391,7 @@
         <v/>
       </c>
       <c r="H4" t="str">
-        <v>威,理,威,情,威,理,威</v>
+        <v>势,策,势,策,势,策,势</v>
       </c>
       <c r="I4" t="str">
         <v>m_ge,m_hao,m_jiang,m_zun</v>
